--- a/마케팅 비용 계산.xlsx
+++ b/마케팅 비용 계산.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mnbv6\Desktop\투캉 공유 폴더\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mnbv6\Desktop\투캉 공용 폴더\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38CFF297-5EF6-4D56-A0C0-DDCDEBD11CAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A016E419-A300-48C6-83A9-982394CD5C2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16230" yWindow="0" windowWidth="22170" windowHeight="20880" xr2:uid="{CAF1035B-39F7-4003-9AD6-DEFCDF622D01}"/>
+    <workbookView xWindow="7200" yWindow="0" windowWidth="14400" windowHeight="12780" xr2:uid="{CAF1035B-39F7-4003-9AD6-DEFCDF622D01}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="52">
   <si>
     <t>국민은행</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -235,6 +235,10 @@
   </si>
   <si>
     <t>광고 수익</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>정기 환불</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -337,7 +341,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -366,6 +370,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -684,7 +691,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2423A38-23FA-43A1-9DAD-825E17572FDC}">
   <dimension ref="A2:P52"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
   <cols>
     <col min="1" max="1" width="22.75" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.5" bestFit="1" customWidth="1"/>
@@ -703,7 +710,7 @@
     <col min="18" max="18" width="9.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -711,7 +718,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.6">
       <c r="B3" t="s">
         <v>2</v>
       </c>
@@ -740,7 +747,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -749,7 +756,7 @@
       </c>
       <c r="K4" s="3"/>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -761,7 +768,7 @@
         <v>58175162</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -773,7 +780,7 @@
         <v>56133162</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -785,7 +792,7 @@
         <v>56064092</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -797,7 +804,7 @@
         <v>55075592</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -819,7 +826,7 @@
         <v>40000000</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -836,7 +843,7 @@
         <v>40000000</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A11" t="s">
         <v>12</v>
       </c>
@@ -852,7 +859,7 @@
         <v>40000000</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A12" t="s">
         <v>13</v>
       </c>
@@ -868,7 +875,7 @@
         <v>40000000</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A13" t="s">
         <v>10</v>
       </c>
@@ -890,7 +897,7 @@
         <v>47500000</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A14" t="s">
         <v>14</v>
       </c>
@@ -906,7 +913,7 @@
         <v>47500000</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A15" t="s">
         <v>15</v>
       </c>
@@ -922,7 +929,7 @@
         <v>47500000</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.6">
       <c r="D16" s="3">
         <v>-40000000</v>
       </c>
@@ -941,7 +948,7 @@
         <v>87500000</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.6">
       <c r="G17" t="s">
         <v>19</v>
       </c>
@@ -957,7 +964,7 @@
         <v>28507</v>
       </c>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.6">
       <c r="A21" t="s">
         <v>22</v>
       </c>
@@ -965,7 +972,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.6">
       <c r="A22" s="5">
         <v>45839</v>
       </c>
@@ -973,7 +980,7 @@
         <v>359700</v>
       </c>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.6">
       <c r="A23" s="5">
         <v>45840</v>
       </c>
@@ -984,7 +991,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.6">
       <c r="A24" s="5">
         <v>45841</v>
       </c>
@@ -998,7 +1005,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.6">
       <c r="A25" s="5">
         <v>45842</v>
       </c>
@@ -1015,7 +1022,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.6">
       <c r="A26" s="5">
         <v>45843</v>
       </c>
@@ -1033,7 +1040,7 @@
         <v>15000000</v>
       </c>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.6">
       <c r="A27" s="5">
         <v>45845</v>
       </c>
@@ -1050,7 +1057,7 @@
         <v>15000000</v>
       </c>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.6">
       <c r="A28" s="5">
         <v>45847</v>
       </c>
@@ -1061,7 +1068,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.6">
       <c r="A29" s="5">
         <v>45848</v>
       </c>
@@ -1072,7 +1079,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.6">
       <c r="A30" s="5">
         <v>45849</v>
       </c>
@@ -1090,10 +1097,10 @@
       </c>
       <c r="P30" s="8">
         <f>M35</f>
-        <v>129416769.55000001</v>
-      </c>
-    </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
+        <v>165012166.55000001</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.6">
       <c r="A31" s="5">
         <v>45850</v>
       </c>
@@ -1101,7 +1108,7 @@
         <v>202400</v>
       </c>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.6">
       <c r="A32" s="5">
         <v>45851</v>
       </c>
@@ -1115,7 +1122,7 @@
         <v>-6000000</v>
       </c>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.6">
       <c r="A33" s="5">
         <v>45852</v>
       </c>
@@ -1132,7 +1139,7 @@
         <v>-4000000</v>
       </c>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.6">
       <c r="A34" s="5">
         <v>45853</v>
       </c>
@@ -1173,7 +1180,7 @@
         <v>-2059610</v>
       </c>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.6">
       <c r="A35" s="5">
         <v>45854</v>
       </c>
@@ -1182,12 +1189,12 @@
       </c>
       <c r="D35" s="3"/>
       <c r="E35" s="3">
-        <f>B52</f>
-        <v>163347823</v>
+        <f>B52+D37</f>
+        <v>205948223</v>
       </c>
       <c r="F35" s="3">
         <f>-E35*0.15</f>
-        <v>-24502173.449999999</v>
+        <v>-30892233.449999999</v>
       </c>
       <c r="G35" s="3">
         <v>0</v>
@@ -1202,15 +1209,14 @@
         <v>-1500000</v>
       </c>
       <c r="K35" s="3">
-        <f>-90000000*0.07</f>
-        <v>-6300000.0000000009</v>
+        <v>-6914943</v>
       </c>
       <c r="L35" s="3">
         <v>12000000</v>
       </c>
       <c r="M35" s="8">
         <f>E35+F35+G35+H35+I35+J35+K35+L35</f>
-        <v>129416769.55000001</v>
+        <v>165012166.55000001</v>
       </c>
       <c r="O35" t="s">
         <v>37</v>
@@ -1219,13 +1225,16 @@
         <v>-25950</v>
       </c>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.6">
       <c r="A36" s="5">
         <v>45855</v>
       </c>
       <c r="B36" s="6">
         <v>10568807</v>
       </c>
+      <c r="D36" t="s">
+        <v>51</v>
+      </c>
       <c r="O36" t="s">
         <v>41</v>
       </c>
@@ -1233,13 +1242,16 @@
         <v>-2590</v>
       </c>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.6">
       <c r="A37" s="5">
         <v>45856</v>
       </c>
       <c r="B37" s="6">
         <v>12560900</v>
       </c>
+      <c r="D37" s="3">
+        <v>-4000000</v>
+      </c>
       <c r="O37" t="s">
         <v>46</v>
       </c>
@@ -1247,7 +1259,7 @@
         <v>-40000000</v>
       </c>
     </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:16" x14ac:dyDescent="0.6">
       <c r="A38" s="5">
         <v>45857</v>
       </c>
@@ -1261,7 +1273,7 @@
         <v>-100000000</v>
       </c>
     </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.6">
       <c r="A39" s="5">
         <v>45858</v>
       </c>
@@ -1275,7 +1287,7 @@
         <v>-988500</v>
       </c>
     </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:16" x14ac:dyDescent="0.6">
       <c r="A40" s="5">
         <v>45859</v>
       </c>
@@ -1290,7 +1302,7 @@
         <v>-110000</v>
       </c>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.6">
       <c r="A41" s="5">
         <v>45860</v>
       </c>
@@ -1298,7 +1310,7 @@
         <v>13438700</v>
       </c>
     </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.6">
       <c r="A42" s="5">
         <v>45861</v>
       </c>
@@ -1310,10 +1322,10 @@
       </c>
       <c r="P42" s="9">
         <f>P30+P32+P33+P34+P35+P36+P37+P38+P39+P40</f>
-        <v>-23769880.449999988</v>
-      </c>
-    </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.3">
+        <v>11825516.550000012</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16" x14ac:dyDescent="0.6">
       <c r="A43" s="5">
         <v>45862</v>
       </c>
@@ -1325,7 +1337,7 @@
       <c r="J43" s="3"/>
       <c r="M43" s="3"/>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.6">
       <c r="A44" s="5">
         <v>45863</v>
       </c>
@@ -1334,7 +1346,7 @@
       </c>
       <c r="H44" s="3"/>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.6">
       <c r="A45" s="5">
         <v>45864</v>
       </c>
@@ -1342,7 +1354,7 @@
         <v>17833200</v>
       </c>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.6">
       <c r="A46" s="5">
         <v>45865</v>
       </c>
@@ -1350,10 +1362,42 @@
         <v>14197700</v>
       </c>
     </row>
-    <row r="52" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:16" x14ac:dyDescent="0.6">
+      <c r="A47" s="5">
+        <v>45866</v>
+      </c>
+      <c r="B47" s="10">
+        <v>15162400</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16" x14ac:dyDescent="0.6">
+      <c r="A48" s="5">
+        <v>45867</v>
+      </c>
+      <c r="B48" s="10">
+        <v>10105700</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.6">
+      <c r="A49" s="5">
+        <v>45868</v>
+      </c>
+      <c r="B49" s="10">
+        <v>10066100</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.6">
+      <c r="A50" s="5">
+        <v>45869</v>
+      </c>
+      <c r="B50" s="10">
+        <v>11266200</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.6">
       <c r="B52" s="7">
         <f>SUM(B22:B51)</f>
-        <v>163347823</v>
+        <v>209948223</v>
       </c>
     </row>
   </sheetData>

--- a/마케팅 비용 계산.xlsx
+++ b/마케팅 비용 계산.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mnbv6\Desktop\투캉 공용 폴더\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mnbv6\Desktop\투캉 공유 폴더\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A016E419-A300-48C6-83A9-982394CD5C2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66F90923-D21F-4396-BEDB-74511D4E2DE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7200" yWindow="0" windowWidth="14400" windowHeight="12780" xr2:uid="{CAF1035B-39F7-4003-9AD6-DEFCDF622D01}"/>
+    <workbookView xWindow="12795" yWindow="0" windowWidth="25605" windowHeight="20880" xr2:uid="{CAF1035B-39F7-4003-9AD6-DEFCDF622D01}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -246,9 +246,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="176" formatCode="&quot;₩&quot;#,##0_);[Red]\(&quot;₩&quot;#,##0\)"/>
+    <numFmt numFmtId="177" formatCode="mm&quot;월&quot;\ dd&quot;일&quot;"/>
   </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
@@ -341,7 +342,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -373,6 +374,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -691,7 +698,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2423A38-23FA-43A1-9DAD-825E17572FDC}">
   <dimension ref="A2:P52"/>
-  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22.75" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.5" bestFit="1" customWidth="1"/>
@@ -710,7 +717,7 @@
     <col min="18" max="18" width="9.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -718,7 +725,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>2</v>
       </c>
@@ -747,7 +754,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -756,7 +763,7 @@
       </c>
       <c r="K4" s="3"/>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -768,7 +775,7 @@
         <v>58175162</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -780,7 +787,7 @@
         <v>56133162</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -792,7 +799,7 @@
         <v>56064092</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -804,7 +811,7 @@
         <v>55075592</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -826,7 +833,7 @@
         <v>40000000</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -843,7 +850,7 @@
         <v>40000000</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>12</v>
       </c>
@@ -859,7 +866,7 @@
         <v>40000000</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>13</v>
       </c>
@@ -875,7 +882,7 @@
         <v>40000000</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>10</v>
       </c>
@@ -897,7 +904,7 @@
         <v>47500000</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>14</v>
       </c>
@@ -913,7 +920,7 @@
         <v>47500000</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>15</v>
       </c>
@@ -929,7 +936,7 @@
         <v>47500000</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="D16" s="3">
         <v>-40000000</v>
       </c>
@@ -948,7 +955,7 @@
         <v>87500000</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.6">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
       <c r="G17" t="s">
         <v>19</v>
       </c>
@@ -964,23 +971,30 @@
         <v>28507</v>
       </c>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.6">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>22</v>
       </c>
       <c r="B21" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.6">
+      <c r="I21" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A22" s="5">
         <v>45839</v>
       </c>
       <c r="B22" s="6">
         <v>359700</v>
       </c>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.6">
+      <c r="I22" s="4">
+        <f>SUM(I4:I16)</f>
+        <v>87500000</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A23" s="5">
         <v>45840</v>
       </c>
@@ -990,8 +1004,14 @@
       <c r="D23" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.6">
+      <c r="H23" s="11">
+        <v>45877</v>
+      </c>
+      <c r="I23" s="4">
+        <v>2600000</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A24" s="5">
         <v>45841</v>
       </c>
@@ -1001,11 +1021,17 @@
       <c r="D24" t="s">
         <v>24</v>
       </c>
+      <c r="H24" s="11">
+        <v>45877</v>
+      </c>
+      <c r="I24" s="4">
+        <v>9000000</v>
+      </c>
       <c r="K24" s="2" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.6">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A25" s="5">
         <v>45842</v>
       </c>
@@ -1015,24 +1041,21 @@
       <c r="D25" t="s">
         <v>25</v>
       </c>
-      <c r="I25" t="s">
-        <v>21</v>
+      <c r="I25" s="12">
+        <f>SUM(I22:I24)</f>
+        <v>99100000</v>
       </c>
       <c r="K25" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.6">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A26" s="5">
         <v>45843</v>
       </c>
       <c r="B26" s="6">
         <v>180400</v>
       </c>
-      <c r="I26" s="4">
-        <f>SUM(I4:I16)</f>
-        <v>87500000</v>
-      </c>
       <c r="K26" t="s">
         <v>27</v>
       </c>
@@ -1040,7 +1063,7 @@
         <v>15000000</v>
       </c>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.6">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A27" s="5">
         <v>45845</v>
       </c>
@@ -1057,7 +1080,7 @@
         <v>15000000</v>
       </c>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.6">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A28" s="5">
         <v>45847</v>
       </c>
@@ -1068,7 +1091,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.6">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A29" s="5">
         <v>45848</v>
       </c>
@@ -1079,7 +1102,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.6">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A30" s="5">
         <v>45849</v>
       </c>
@@ -1100,7 +1123,7 @@
         <v>165012166.55000001</v>
       </c>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.6">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A31" s="5">
         <v>45850</v>
       </c>
@@ -1108,7 +1131,7 @@
         <v>202400</v>
       </c>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.6">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A32" s="5">
         <v>45851</v>
       </c>
@@ -1122,7 +1145,7 @@
         <v>-6000000</v>
       </c>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.6">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A33" s="5">
         <v>45852</v>
       </c>
@@ -1139,7 +1162,7 @@
         <v>-4000000</v>
       </c>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.6">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A34" s="5">
         <v>45853</v>
       </c>
@@ -1180,7 +1203,7 @@
         <v>-2059610</v>
       </c>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.6">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A35" s="5">
         <v>45854</v>
       </c>
@@ -1225,7 +1248,7 @@
         <v>-25950</v>
       </c>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.6">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A36" s="5">
         <v>45855</v>
       </c>
@@ -1242,7 +1265,7 @@
         <v>-2590</v>
       </c>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.6">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A37" s="5">
         <v>45856</v>
       </c>
@@ -1259,7 +1282,7 @@
         <v>-40000000</v>
       </c>
     </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.6">
+    <row r="38" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A38" s="5">
         <v>45857</v>
       </c>
@@ -1273,7 +1296,7 @@
         <v>-100000000</v>
       </c>
     </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.6">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A39" s="5">
         <v>45858</v>
       </c>
@@ -1287,7 +1310,7 @@
         <v>-988500</v>
       </c>
     </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.6">
+    <row r="40" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A40" s="5">
         <v>45859</v>
       </c>
@@ -1302,7 +1325,7 @@
         <v>-110000</v>
       </c>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.6">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A41" s="5">
         <v>45860</v>
       </c>
@@ -1310,7 +1333,7 @@
         <v>13438700</v>
       </c>
     </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.6">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A42" s="5">
         <v>45861</v>
       </c>
@@ -1325,7 +1348,7 @@
         <v>11825516.550000012</v>
       </c>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.6">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A43" s="5">
         <v>45862</v>
       </c>
@@ -1337,7 +1360,7 @@
       <c r="J43" s="3"/>
       <c r="M43" s="3"/>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.6">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A44" s="5">
         <v>45863</v>
       </c>
@@ -1346,7 +1369,7 @@
       </c>
       <c r="H44" s="3"/>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.6">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A45" s="5">
         <v>45864</v>
       </c>
@@ -1354,7 +1377,7 @@
         <v>17833200</v>
       </c>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.6">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A46" s="5">
         <v>45865</v>
       </c>
@@ -1362,7 +1385,7 @@
         <v>14197700</v>
       </c>
     </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.6">
+    <row r="47" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A47" s="5">
         <v>45866</v>
       </c>
@@ -1370,7 +1393,7 @@
         <v>15162400</v>
       </c>
     </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.6">
+    <row r="48" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A48" s="5">
         <v>45867</v>
       </c>
@@ -1378,7 +1401,7 @@
         <v>10105700</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" s="5">
         <v>45868</v>
       </c>
@@ -1386,7 +1409,7 @@
         <v>10066100</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" s="5">
         <v>45869</v>
       </c>
@@ -1394,7 +1417,7 @@
         <v>11266200</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B52" s="7">
         <f>SUM(B22:B51)</f>
         <v>209948223</v>

--- a/마케팅 비용 계산.xlsx
+++ b/마케팅 비용 계산.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mnbv6\Desktop\투캉 공유 폴더\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mnbv6\Desktop\투캉 공용 폴더\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66F90923-D21F-4396-BEDB-74511D4E2DE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EED8730-123F-4F96-B624-5D10D31F78E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12795" yWindow="0" windowWidth="25605" windowHeight="20880" xr2:uid="{CAF1035B-39F7-4003-9AD6-DEFCDF622D01}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{CAF1035B-39F7-4003-9AD6-DEFCDF622D01}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="53">
   <si>
     <t>국민은행</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -239,6 +239,10 @@
   </si>
   <si>
     <t>정기 환불</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>광고수익</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -698,7 +702,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2423A38-23FA-43A1-9DAD-825E17572FDC}">
   <dimension ref="A2:P52"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
   <cols>
     <col min="1" max="1" width="22.75" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.5" bestFit="1" customWidth="1"/>
@@ -717,7 +721,7 @@
     <col min="18" max="18" width="9.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -725,7 +729,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.6">
       <c r="B3" t="s">
         <v>2</v>
       </c>
@@ -754,7 +758,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -763,7 +767,7 @@
       </c>
       <c r="K4" s="3"/>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -775,7 +779,7 @@
         <v>58175162</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -787,7 +791,7 @@
         <v>56133162</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -799,7 +803,7 @@
         <v>56064092</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -811,7 +815,7 @@
         <v>55075592</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -833,7 +837,7 @@
         <v>40000000</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -850,7 +854,7 @@
         <v>40000000</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A11" t="s">
         <v>12</v>
       </c>
@@ -866,7 +870,7 @@
         <v>40000000</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A12" t="s">
         <v>13</v>
       </c>
@@ -882,7 +886,7 @@
         <v>40000000</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A13" t="s">
         <v>10</v>
       </c>
@@ -904,7 +908,7 @@
         <v>47500000</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A14" t="s">
         <v>14</v>
       </c>
@@ -920,7 +924,7 @@
         <v>47500000</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A15" t="s">
         <v>15</v>
       </c>
@@ -936,7 +940,7 @@
         <v>47500000</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.6">
       <c r="D16" s="3">
         <v>-40000000</v>
       </c>
@@ -955,7 +959,7 @@
         <v>87500000</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.6">
       <c r="G17" t="s">
         <v>19</v>
       </c>
@@ -971,7 +975,7 @@
         <v>28507</v>
       </c>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.6">
       <c r="A21" t="s">
         <v>22</v>
       </c>
@@ -982,7 +986,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.6">
       <c r="A22" s="5">
         <v>45839</v>
       </c>
@@ -994,7 +998,7 @@
         <v>87500000</v>
       </c>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.6">
       <c r="A23" s="5">
         <v>45840</v>
       </c>
@@ -1011,7 +1015,7 @@
         <v>2600000</v>
       </c>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.6">
       <c r="A24" s="5">
         <v>45841</v>
       </c>
@@ -1030,8 +1034,14 @@
       <c r="K24" s="2" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="O24" t="s">
+        <v>44</v>
+      </c>
+      <c r="P24" s="8">
+        <v>174000000</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.6">
       <c r="A25" s="5">
         <v>45842</v>
       </c>
@@ -1048,8 +1058,14 @@
       <c r="K25" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="O25" t="s">
+        <v>26</v>
+      </c>
+      <c r="P25" s="8">
+        <v>30000000</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.6">
       <c r="A26" s="5">
         <v>45843</v>
       </c>
@@ -1062,8 +1078,14 @@
       <c r="L26" s="3">
         <v>15000000</v>
       </c>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="O26" t="s">
+        <v>52</v>
+      </c>
+      <c r="P26" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.6">
       <c r="A27" s="5">
         <v>45845</v>
       </c>
@@ -1080,7 +1102,7 @@
         <v>15000000</v>
       </c>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.6">
       <c r="A28" s="5">
         <v>45847</v>
       </c>
@@ -1090,8 +1112,14 @@
       <c r="D28" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="O28" t="s">
+        <v>7</v>
+      </c>
+      <c r="P28" s="3">
+        <v>-1500000</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.6">
       <c r="A29" s="5">
         <v>45848</v>
       </c>
@@ -1101,8 +1129,14 @@
       <c r="K29" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="O29" t="s">
+        <v>30</v>
+      </c>
+      <c r="P29" s="3">
+        <v>-38628880</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.6">
       <c r="A30" s="5">
         <v>45849</v>
       </c>
@@ -1116,14 +1150,13 @@
         <v>-38628880</v>
       </c>
       <c r="O30" t="s">
-        <v>44</v>
-      </c>
-      <c r="P30" s="8">
-        <f>M35</f>
-        <v>165012166.55000001</v>
-      </c>
-    </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
+        <v>35</v>
+      </c>
+      <c r="P30" s="3">
+        <v>-6914943</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.6">
       <c r="A31" s="5">
         <v>45850</v>
       </c>
@@ -1131,7 +1164,7 @@
         <v>202400</v>
       </c>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.6">
       <c r="A32" s="5">
         <v>45851</v>
       </c>
@@ -1145,7 +1178,7 @@
         <v>-6000000</v>
       </c>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.6">
       <c r="A33" s="5">
         <v>45852</v>
       </c>
@@ -1162,7 +1195,7 @@
         <v>-4000000</v>
       </c>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.6">
       <c r="A34" s="5">
         <v>45853</v>
       </c>
@@ -1203,7 +1236,7 @@
         <v>-2059610</v>
       </c>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.6">
       <c r="A35" s="5">
         <v>45854</v>
       </c>
@@ -1248,7 +1281,7 @@
         <v>-25950</v>
       </c>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.6">
       <c r="A36" s="5">
         <v>45855</v>
       </c>
@@ -1265,7 +1298,7 @@
         <v>-2590</v>
       </c>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.6">
       <c r="A37" s="5">
         <v>45856</v>
       </c>
@@ -1282,7 +1315,7 @@
         <v>-40000000</v>
       </c>
     </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:16" x14ac:dyDescent="0.6">
       <c r="A38" s="5">
         <v>45857</v>
       </c>
@@ -1296,7 +1329,7 @@
         <v>-100000000</v>
       </c>
     </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.6">
       <c r="A39" s="5">
         <v>45858</v>
       </c>
@@ -1310,7 +1343,7 @@
         <v>-988500</v>
       </c>
     </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:16" x14ac:dyDescent="0.6">
       <c r="A40" s="5">
         <v>45859</v>
       </c>
@@ -1325,7 +1358,7 @@
         <v>-110000</v>
       </c>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.6">
       <c r="A41" s="5">
         <v>45860</v>
       </c>
@@ -1333,7 +1366,7 @@
         <v>13438700</v>
       </c>
     </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.6">
       <c r="A42" s="5">
         <v>45861</v>
       </c>
@@ -1344,11 +1377,11 @@
         <v>45</v>
       </c>
       <c r="P42" s="9">
-        <f>P30+P32+P33+P34+P35+P36+P37+P38+P39+P40</f>
-        <v>11825516.550000012</v>
-      </c>
-    </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.3">
+        <f>P24+P25+P28+P29+P30+P32+P33+P34+P35+P36+P37+P38+P39+P40</f>
+        <v>3769527</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16" x14ac:dyDescent="0.6">
       <c r="A43" s="5">
         <v>45862</v>
       </c>
@@ -1360,7 +1393,7 @@
       <c r="J43" s="3"/>
       <c r="M43" s="3"/>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.6">
       <c r="A44" s="5">
         <v>45863</v>
       </c>
@@ -1369,7 +1402,7 @@
       </c>
       <c r="H44" s="3"/>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.6">
       <c r="A45" s="5">
         <v>45864</v>
       </c>
@@ -1377,7 +1410,7 @@
         <v>17833200</v>
       </c>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.6">
       <c r="A46" s="5">
         <v>45865</v>
       </c>
@@ -1385,7 +1418,7 @@
         <v>14197700</v>
       </c>
     </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:16" x14ac:dyDescent="0.6">
       <c r="A47" s="5">
         <v>45866</v>
       </c>
@@ -1393,7 +1426,7 @@
         <v>15162400</v>
       </c>
     </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:16" x14ac:dyDescent="0.6">
       <c r="A48" s="5">
         <v>45867</v>
       </c>
@@ -1401,7 +1434,7 @@
         <v>10105700</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A49" s="5">
         <v>45868</v>
       </c>
@@ -1409,7 +1442,7 @@
         <v>10066100</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A50" s="5">
         <v>45869</v>
       </c>
@@ -1417,7 +1450,7 @@
         <v>11266200</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.6">
       <c r="B52" s="7">
         <f>SUM(B22:B51)</f>
         <v>209948223</v>

--- a/마케팅 비용 계산.xlsx
+++ b/마케팅 비용 계산.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mnbv6\Desktop\투캉 공용 폴더\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mnbv6\Desktop\투캉 공유 폴더\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EED8730-123F-4F96-B624-5D10D31F78E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2261EA8E-8041-4CC6-8360-1ABE9A2DD587}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{CAF1035B-39F7-4003-9AD6-DEFCDF622D01}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28980" windowHeight="20880" xr2:uid="{CAF1035B-39F7-4003-9AD6-DEFCDF622D01}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="56">
   <si>
     <t>국민은행</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -238,11 +238,23 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>정기 환불</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>광고수익</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>실제지급</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>지급완료</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>08월 16일</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>팽글</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -346,7 +358,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -385,6 +397,12 @@
     </xf>
     <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -701,15 +719,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2423A38-23FA-43A1-9DAD-825E17572FDC}">
-  <dimension ref="A2:P52"/>
-  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
+  <dimension ref="A2:Q57"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22.75" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.5" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="19.75" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13.625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="18.625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="15.875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14.25" bestFit="1" customWidth="1"/>
@@ -717,11 +735,11 @@
     <col min="11" max="11" width="15.875" bestFit="1" customWidth="1"/>
     <col min="12" max="13" width="13.625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="9.625" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.25" bestFit="1" customWidth="1"/>
+    <col min="15" max="17" width="14.25" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="9.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -729,7 +747,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>2</v>
       </c>
@@ -757,8 +775,11 @@
       <c r="L3" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.6">
+      <c r="O3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -766,8 +787,12 @@
         <v>8175162</v>
       </c>
       <c r="K4" s="3"/>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.6">
+      <c r="O4" s="4">
+        <f>SUM(I4:I16)</f>
+        <v>87500000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -778,8 +803,14 @@
         <f>E4+B5+C5</f>
         <v>58175162</v>
       </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.6">
+      <c r="N5" s="11">
+        <v>45877</v>
+      </c>
+      <c r="O5" s="4">
+        <v>2600000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -790,8 +821,14 @@
         <f>E5+B6+C6</f>
         <v>56133162</v>
       </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.6">
+      <c r="N6" s="11">
+        <v>45877</v>
+      </c>
+      <c r="O6" s="4">
+        <v>9000000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -802,8 +839,11 @@
         <f t="shared" ref="E7:E8" si="0">E6+B7+C7</f>
         <v>56064092</v>
       </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.6">
+      <c r="O7" s="4">
+        <v>5000000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -814,8 +854,14 @@
         <f t="shared" si="0"/>
         <v>55075592</v>
       </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.6">
+      <c r="P8" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q8" s="4">
+        <v>70000000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -836,8 +882,12 @@
         <f>K8+H9+I9+J9</f>
         <v>40000000</v>
       </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.6">
+      <c r="O9" s="12">
+        <f>SUM(O4:O8)</f>
+        <v>104100000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -854,7 +904,7 @@
         <v>40000000</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>12</v>
       </c>
@@ -870,7 +920,7 @@
         <v>40000000</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>13</v>
       </c>
@@ -886,7 +936,7 @@
         <v>40000000</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>10</v>
       </c>
@@ -908,7 +958,7 @@
         <v>47500000</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>14</v>
       </c>
@@ -924,7 +974,7 @@
         <v>47500000</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>15</v>
       </c>
@@ -940,7 +990,7 @@
         <v>47500000</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
       <c r="D16" s="3">
         <v>-40000000</v>
       </c>
@@ -959,7 +1009,7 @@
         <v>87500000</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.6">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="G17" t="s">
         <v>19</v>
       </c>
@@ -975,30 +1025,23 @@
         <v>28507</v>
       </c>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.6">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>22</v>
       </c>
       <c r="B21" t="s">
         <v>23</v>
       </c>
-      <c r="I21" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.6">
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" s="5">
         <v>45839</v>
       </c>
       <c r="B22" s="6">
         <v>359700</v>
       </c>
-      <c r="I22" s="4">
-        <f>SUM(I4:I16)</f>
-        <v>87500000</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.6">
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" s="5">
         <v>45840</v>
       </c>
@@ -1008,14 +1051,8 @@
       <c r="D23" t="s">
         <v>38</v>
       </c>
-      <c r="H23" s="11">
-        <v>45877</v>
-      </c>
-      <c r="I23" s="4">
-        <v>2600000</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.6">
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" s="5">
         <v>45841</v>
       </c>
@@ -1025,23 +1062,11 @@
       <c r="D24" t="s">
         <v>24</v>
       </c>
-      <c r="H24" s="11">
-        <v>45877</v>
-      </c>
-      <c r="I24" s="4">
-        <v>9000000</v>
-      </c>
       <c r="K24" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="O24" t="s">
-        <v>44</v>
-      </c>
-      <c r="P24" s="8">
-        <v>174000000</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.6">
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" s="5">
         <v>45842</v>
       </c>
@@ -1051,21 +1076,11 @@
       <c r="D25" t="s">
         <v>25</v>
       </c>
-      <c r="I25" s="12">
-        <f>SUM(I22:I24)</f>
-        <v>99100000</v>
-      </c>
       <c r="K25" t="s">
         <v>26</v>
       </c>
-      <c r="O25" t="s">
-        <v>26</v>
-      </c>
-      <c r="P25" s="8">
-        <v>30000000</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.6">
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" s="5">
         <v>45843</v>
       </c>
@@ -1078,14 +1093,8 @@
       <c r="L26" s="3">
         <v>15000000</v>
       </c>
-      <c r="O26" t="s">
-        <v>52</v>
-      </c>
-      <c r="P26" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.6">
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" s="5">
         <v>45845</v>
       </c>
@@ -1102,7 +1111,7 @@
         <v>15000000</v>
       </c>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.6">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" s="5">
         <v>45847</v>
       </c>
@@ -1112,14 +1121,8 @@
       <c r="D28" t="s">
         <v>40</v>
       </c>
-      <c r="O28" t="s">
-        <v>7</v>
-      </c>
-      <c r="P28" s="3">
-        <v>-1500000</v>
-      </c>
-    </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.6">
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" s="5">
         <v>45848</v>
       </c>
@@ -1129,14 +1132,8 @@
       <c r="K29" t="s">
         <v>29</v>
       </c>
-      <c r="O29" t="s">
-        <v>30</v>
-      </c>
-      <c r="P29" s="3">
-        <v>-38628880</v>
-      </c>
-    </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.6">
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" s="5">
         <v>45849</v>
       </c>
@@ -1149,14 +1146,8 @@
       <c r="L30" s="3">
         <v>-38628880</v>
       </c>
-      <c r="O30" t="s">
-        <v>35</v>
-      </c>
-      <c r="P30" s="3">
-        <v>-6914943</v>
-      </c>
-    </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.6">
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" s="5">
         <v>45850</v>
       </c>
@@ -1164,21 +1155,15 @@
         <v>202400</v>
       </c>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.6">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" s="5">
         <v>45851</v>
       </c>
       <c r="B32" s="6">
         <v>20900</v>
       </c>
-      <c r="O32" t="s">
-        <v>42</v>
-      </c>
-      <c r="P32" s="3">
-        <v>-6000000</v>
-      </c>
-    </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.6">
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A33" s="5">
         <v>45852</v>
       </c>
@@ -1188,14 +1173,8 @@
       <c r="E33" t="s">
         <v>33</v>
       </c>
-      <c r="O33" t="s">
-        <v>43</v>
-      </c>
-      <c r="P33" s="3">
-        <v>-4000000</v>
-      </c>
-    </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.6">
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A34" s="5">
         <v>45853</v>
       </c>
@@ -1229,14 +1208,8 @@
       <c r="M34" t="s">
         <v>34</v>
       </c>
-      <c r="O34" t="s">
-        <v>36</v>
-      </c>
-      <c r="P34" s="3">
-        <v>-2059610</v>
-      </c>
-    </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.6">
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A35" s="5">
         <v>45854</v>
       </c>
@@ -1246,11 +1219,11 @@
       <c r="D35" s="3"/>
       <c r="E35" s="3">
         <f>B52+D37</f>
-        <v>205948223</v>
+        <v>209948223</v>
       </c>
       <c r="F35" s="3">
         <f>-E35*0.15</f>
-        <v>-30892233.449999999</v>
+        <v>-31492233.449999999</v>
       </c>
       <c r="G35" s="3">
         <v>0</v>
@@ -1272,78 +1245,55 @@
       </c>
       <c r="M35" s="8">
         <f>E35+F35+G35+H35+I35+J35+K35+L35</f>
-        <v>165012166.55000001</v>
-      </c>
-      <c r="O35" t="s">
-        <v>37</v>
-      </c>
-      <c r="P35" s="3">
-        <v>-25950</v>
-      </c>
-    </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.6">
+        <v>168412166.55000001</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A36" s="5">
         <v>45855</v>
       </c>
       <c r="B36" s="6">
         <v>10568807</v>
       </c>
-      <c r="D36" t="s">
-        <v>51</v>
-      </c>
-      <c r="O36" t="s">
-        <v>41</v>
-      </c>
-      <c r="P36" s="3">
-        <v>-2590</v>
-      </c>
-    </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.6">
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A37" s="5">
         <v>45856</v>
       </c>
       <c r="B37" s="6">
         <v>12560900</v>
       </c>
-      <c r="D37" s="3">
-        <v>-4000000</v>
-      </c>
-      <c r="O37" t="s">
-        <v>46</v>
-      </c>
-      <c r="P37" s="3">
-        <v>-40000000</v>
-      </c>
-    </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.6">
+      <c r="D37" s="3"/>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A38" s="5">
         <v>45857</v>
       </c>
       <c r="B38" s="6">
         <v>18991500</v>
       </c>
-      <c r="O38" t="s">
-        <v>47</v>
-      </c>
-      <c r="P38" s="3">
-        <v>-100000000</v>
-      </c>
-    </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.6">
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A39" s="5">
         <v>45858</v>
       </c>
       <c r="B39" s="6">
         <v>17752900</v>
       </c>
-      <c r="O39" t="s">
-        <v>48</v>
-      </c>
-      <c r="P39" s="3">
-        <v>-988500</v>
-      </c>
-    </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.6">
+      <c r="E39" t="s">
+        <v>44</v>
+      </c>
+      <c r="F39" s="8">
+        <v>174000000</v>
+      </c>
+      <c r="H39" t="s">
+        <v>52</v>
+      </c>
+      <c r="I39" s="8">
+        <v>174000000</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A40" s="5">
         <v>45859</v>
       </c>
@@ -1351,109 +1301,287 @@
         <v>13028400</v>
       </c>
       <c r="D40" s="3"/>
-      <c r="O40" t="s">
-        <v>49</v>
-      </c>
-      <c r="P40" s="3">
-        <v>-110000</v>
-      </c>
-    </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.6">
+      <c r="E40" t="s">
+        <v>26</v>
+      </c>
+      <c r="F40" s="8">
+        <v>30000000</v>
+      </c>
+      <c r="H40" t="s">
+        <v>42</v>
+      </c>
+      <c r="I40" s="3">
+        <v>-11000000</v>
+      </c>
+      <c r="J40" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A41" s="5">
         <v>45860</v>
       </c>
       <c r="B41" s="6">
         <v>13438700</v>
       </c>
-    </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.6">
+      <c r="E41" t="s">
+        <v>51</v>
+      </c>
+      <c r="F41" s="8">
+        <v>0</v>
+      </c>
+      <c r="H41" t="s">
+        <v>43</v>
+      </c>
+      <c r="I41" s="3">
+        <v>-4000000</v>
+      </c>
+      <c r="J41" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A42" s="5">
         <v>45861</v>
       </c>
       <c r="B42" s="6">
         <v>12865616</v>
       </c>
-      <c r="O42" t="s">
-        <v>45</v>
-      </c>
-      <c r="P42" s="9">
-        <f>P24+P25+P28+P29+P30+P32+P33+P34+P35+P36+P37+P38+P39+P40</f>
-        <v>3769527</v>
-      </c>
-    </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.6">
+      <c r="H42" t="s">
+        <v>36</v>
+      </c>
+      <c r="I42" s="3">
+        <v>-2059610</v>
+      </c>
+      <c r="J42" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A43" s="5">
         <v>45862</v>
       </c>
       <c r="B43" s="6">
         <v>12641200</v>
+      </c>
+      <c r="E43" t="s">
+        <v>7</v>
+      </c>
+      <c r="F43" s="3">
+        <v>-1500000</v>
       </c>
       <c r="H43" s="3"/>
       <c r="I43" s="3"/>
       <c r="J43" s="3"/>
       <c r="M43" s="3"/>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.6">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A44" s="5">
         <v>45863</v>
       </c>
       <c r="B44" s="6">
         <v>14798300</v>
       </c>
-      <c r="H44" s="3"/>
-    </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.6">
+      <c r="E44" t="s">
+        <v>30</v>
+      </c>
+      <c r="F44" s="3">
+        <v>-38628880</v>
+      </c>
+      <c r="H44" t="s">
+        <v>7</v>
+      </c>
+      <c r="I44" s="3">
+        <v>-1500000</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A45" s="5">
         <v>45864</v>
       </c>
       <c r="B45" s="6">
         <v>17833200</v>
       </c>
-    </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.6">
+      <c r="E45" t="s">
+        <v>35</v>
+      </c>
+      <c r="F45" s="3">
+        <v>-6914943</v>
+      </c>
+      <c r="H45" t="s">
+        <v>35</v>
+      </c>
+      <c r="I45" s="3">
+        <v>-6686763</v>
+      </c>
+      <c r="J45" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A46" s="5">
         <v>45865</v>
       </c>
       <c r="B46" s="6">
         <v>14197700</v>
       </c>
-    </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.6">
+      <c r="H46" t="s">
+        <v>30</v>
+      </c>
+      <c r="I46" s="3">
+        <v>-26002768</v>
+      </c>
+      <c r="J46" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A47" s="5">
         <v>45866</v>
       </c>
       <c r="B47" s="10">
         <v>15162400</v>
       </c>
-    </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.6">
+      <c r="E47" t="s">
+        <v>42</v>
+      </c>
+      <c r="F47" s="3">
+        <v>-6000000</v>
+      </c>
+      <c r="H47" t="s">
+        <v>47</v>
+      </c>
+      <c r="I47" s="3">
+        <v>-70000000</v>
+      </c>
+      <c r="J47" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A48" s="5">
         <v>45867</v>
       </c>
       <c r="B48" s="10">
         <v>10105700</v>
       </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.6">
+      <c r="E48" t="s">
+        <v>43</v>
+      </c>
+      <c r="F48" s="3">
+        <v>-4000000</v>
+      </c>
+      <c r="H48" t="s">
+        <v>47</v>
+      </c>
+      <c r="I48" s="3">
+        <v>-30000000</v>
+      </c>
+      <c r="J48" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49" s="5">
         <v>45868</v>
       </c>
       <c r="B49" s="10">
         <v>10066100</v>
       </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.6">
+      <c r="E49" t="s">
+        <v>36</v>
+      </c>
+      <c r="F49" s="3">
+        <v>-2059610</v>
+      </c>
+      <c r="H49" t="s">
+        <v>46</v>
+      </c>
+      <c r="I49" s="3">
+        <v>-20000000</v>
+      </c>
+      <c r="J49" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50" s="5">
         <v>45869</v>
       </c>
       <c r="B50" s="10">
         <v>11266200</v>
       </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.6">
+      <c r="E50" t="s">
+        <v>37</v>
+      </c>
+      <c r="F50" s="3">
+        <v>-25950</v>
+      </c>
+      <c r="H50" t="s">
+        <v>55</v>
+      </c>
+      <c r="I50" s="8">
+        <v>2590995</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="E51" t="s">
+        <v>41</v>
+      </c>
+      <c r="F51" s="3">
+        <v>-2590</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B52" s="7">
         <f>SUM(B22:B51)</f>
         <v>209948223</v>
+      </c>
+      <c r="E52" t="s">
+        <v>46</v>
+      </c>
+      <c r="F52" s="3">
+        <v>-40000000</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="E53" t="s">
+        <v>47</v>
+      </c>
+      <c r="F53" s="3">
+        <v>-100000000</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="E54" t="s">
+        <v>48</v>
+      </c>
+      <c r="F54" s="3">
+        <v>-988500</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="E55" t="s">
+        <v>49</v>
+      </c>
+      <c r="F55" s="3">
+        <v>-110000</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="E57" t="s">
+        <v>45</v>
+      </c>
+      <c r="F57" s="9">
+        <f>F39+F40+F43+F44+F45+F47+F48+F49+F50+F51+F52+F53+F54+F55</f>
+        <v>3769527</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="I57" s="13">
+        <f>SUM(I39:I55)</f>
+        <v>5341854</v>
       </c>
     </row>
   </sheetData>

--- a/마케팅 비용 계산.xlsx
+++ b/마케팅 비용 계산.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mnbv6\Desktop\투캉 공유 폴더\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2261EA8E-8041-4CC6-8360-1ABE9A2DD587}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3584AAA4-3225-44A4-A2C9-27B12C5A6381}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28980" windowHeight="20880" xr2:uid="{CAF1035B-39F7-4003-9AD6-DEFCDF622D01}"/>
+    <workbookView xWindow="12795" yWindow="0" windowWidth="25605" windowHeight="20880" xr2:uid="{CAF1035B-39F7-4003-9AD6-DEFCDF622D01}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="60">
   <si>
     <t>국민은행</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -255,6 +255,22 @@
   </si>
   <si>
     <t>팽글</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>8월1일~8월31일</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>구글 수익</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>원스토어 수익</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>부가세 준비(10%)</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -262,12 +278,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="4">
+    <numFmt numFmtId="6" formatCode="&quot;₩&quot;#,##0;[Red]\-&quot;₩&quot;#,##0"/>
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="176" formatCode="&quot;₩&quot;#,##0_);[Red]\(&quot;₩&quot;#,##0\)"/>
     <numFmt numFmtId="177" formatCode="mm&quot;월&quot;\ dd&quot;일&quot;"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -326,6 +343,23 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF0070C0"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF0070C0"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -358,7 +392,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -403,6 +437,18 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="6" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="6" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -719,19 +765,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2423A38-23FA-43A1-9DAD-825E17572FDC}">
-  <dimension ref="A2:Q57"/>
+  <dimension ref="A2:Q81"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22.75" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="19.75" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.25" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14.875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="18.625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="15.875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14.25" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="15.875" bestFit="1" customWidth="1"/>
     <col min="12" max="13" width="13.625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="9.625" bestFit="1" customWidth="1"/>
@@ -1481,7 +1527,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A49" s="5">
         <v>45868</v>
       </c>
@@ -1504,7 +1550,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A50" s="5">
         <v>45869</v>
       </c>
@@ -1524,7 +1570,7 @@
         <v>2590995</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:13" x14ac:dyDescent="0.3">
       <c r="E51" t="s">
         <v>41</v>
       </c>
@@ -1532,7 +1578,7 @@
         <v>-2590</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B52" s="7">
         <f>SUM(B22:B51)</f>
         <v>209948223</v>
@@ -1544,7 +1590,7 @@
         <v>-40000000</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:13" x14ac:dyDescent="0.3">
       <c r="E53" t="s">
         <v>47</v>
       </c>
@@ -1552,7 +1598,7 @@
         <v>-100000000</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:13" x14ac:dyDescent="0.3">
       <c r="E54" t="s">
         <v>48</v>
       </c>
@@ -1560,7 +1606,7 @@
         <v>-988500</v>
       </c>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:13" x14ac:dyDescent="0.3">
       <c r="E55" t="s">
         <v>49</v>
       </c>
@@ -1568,7 +1614,7 @@
         <v>-110000</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:13" x14ac:dyDescent="0.3">
       <c r="E57" t="s">
         <v>45</v>
       </c>
@@ -1582,6 +1628,135 @@
       <c r="I57" s="13">
         <f>SUM(I39:I55)</f>
         <v>5341854</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="C63" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F63" s="3"/>
+      <c r="M63" s="8"/>
+    </row>
+    <row r="64" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="C64" t="s">
+        <v>57</v>
+      </c>
+      <c r="D64" s="17">
+        <v>161859380</v>
+      </c>
+    </row>
+    <row r="65" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C65" t="s">
+        <v>58</v>
+      </c>
+      <c r="D65" s="18">
+        <v>12313067</v>
+      </c>
+    </row>
+    <row r="66" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C66" t="s">
+        <v>50</v>
+      </c>
+      <c r="D66" s="18">
+        <v>5000000</v>
+      </c>
+    </row>
+    <row r="68" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C68" t="s">
+        <v>16</v>
+      </c>
+      <c r="D68" s="3">
+        <v>-99000000</v>
+      </c>
+    </row>
+    <row r="69" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C69" t="s">
+        <v>7</v>
+      </c>
+      <c r="D69" s="3">
+        <v>-2000000</v>
+      </c>
+    </row>
+    <row r="70" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C70" t="s">
+        <v>35</v>
+      </c>
+      <c r="D70" s="3">
+        <v>-6930000</v>
+      </c>
+    </row>
+    <row r="72" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C72" t="s">
+        <v>42</v>
+      </c>
+      <c r="D72" s="3">
+        <v>-6000000</v>
+      </c>
+    </row>
+    <row r="73" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C73" t="s">
+        <v>43</v>
+      </c>
+      <c r="D73" s="3">
+        <v>-4000000</v>
+      </c>
+    </row>
+    <row r="74" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C74" t="s">
+        <v>36</v>
+      </c>
+      <c r="D74" s="3">
+        <v>-2059610</v>
+      </c>
+    </row>
+    <row r="75" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C75" t="s">
+        <v>37</v>
+      </c>
+      <c r="D75" s="3">
+        <v>-25950</v>
+      </c>
+    </row>
+    <row r="76" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C76" t="s">
+        <v>41</v>
+      </c>
+      <c r="D76" s="3">
+        <v>-2590</v>
+      </c>
+    </row>
+    <row r="77" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C77" t="s">
+        <v>48</v>
+      </c>
+      <c r="D77" s="3">
+        <v>-988500</v>
+      </c>
+    </row>
+    <row r="78" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C78" t="s">
+        <v>49</v>
+      </c>
+      <c r="D78" s="3">
+        <v>-110000</v>
+      </c>
+    </row>
+    <row r="79" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C79" t="s">
+        <v>59</v>
+      </c>
+      <c r="D79" s="15">
+        <f>-(D64+D65)*0.1</f>
+        <v>-17417244.699999999</v>
+      </c>
+    </row>
+    <row r="81" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C81" t="s">
+        <v>45</v>
+      </c>
+      <c r="D81" s="16">
+        <f>SUM(D64:D79)</f>
+        <v>40638552.299999997</v>
       </c>
     </row>
   </sheetData>

--- a/마케팅 비용 계산.xlsx
+++ b/마케팅 비용 계산.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mnbv6\Desktop\투캉 공유 폴더\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3584AAA4-3225-44A4-A2C9-27B12C5A6381}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{453A4A39-9FDA-4B43-A0AA-C1641DED2B7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12795" yWindow="0" windowWidth="25605" windowHeight="20880" xr2:uid="{CAF1035B-39F7-4003-9AD6-DEFCDF622D01}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="20880" xr2:uid="{CAF1035B-39F7-4003-9AD6-DEFCDF622D01}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="64">
   <si>
     <t>국민은행</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -271,6 +271,22 @@
   </si>
   <si>
     <t>부가세 준비(10%)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>통잔 잔고</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>일반신용대출</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>미지급</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>지급</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -284,7 +300,7 @@
     <numFmt numFmtId="176" formatCode="&quot;₩&quot;#,##0_);[Red]\(&quot;₩&quot;#,##0\)"/>
     <numFmt numFmtId="177" formatCode="mm&quot;월&quot;\ dd&quot;일&quot;"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -360,6 +376,14 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1" tint="0.34998626667073579"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -392,7 +416,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -448,6 +472,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -765,7 +792,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2423A38-23FA-43A1-9DAD-825E17572FDC}">
-  <dimension ref="A2:Q81"/>
+  <dimension ref="A2:Q86"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22.75" bestFit="1" customWidth="1"/>
@@ -1630,14 +1657,28 @@
         <v>5341854</v>
       </c>
     </row>
+    <row r="62" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="C62" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
     <row r="63" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="C63" s="2" t="s">
-        <v>56</v>
+      <c r="B63" t="s">
+        <v>63</v>
+      </c>
+      <c r="C63" t="s">
+        <v>60</v>
+      </c>
+      <c r="D63" s="18">
+        <v>7526335</v>
       </c>
       <c r="F63" s="3"/>
       <c r="M63" s="8"/>
     </row>
     <row r="64" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B64" t="s">
+        <v>63</v>
+      </c>
       <c r="C64" t="s">
         <v>57</v>
       </c>
@@ -1645,118 +1686,157 @@
         <v>161859380</v>
       </c>
     </row>
-    <row r="65" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:5" x14ac:dyDescent="0.3">
       <c r="C65" t="s">
         <v>58</v>
       </c>
-      <c r="D65" s="18">
+      <c r="E65" s="18">
         <v>12313067</v>
       </c>
     </row>
-    <row r="66" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:5" x14ac:dyDescent="0.3">
       <c r="C66" t="s">
         <v>50</v>
       </c>
-      <c r="D66" s="18">
-        <v>5000000</v>
-      </c>
-    </row>
-    <row r="68" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="D66" s="18"/>
+    </row>
+    <row r="68" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B68" t="s">
+        <v>63</v>
+      </c>
       <c r="C68" t="s">
         <v>16</v>
       </c>
       <c r="D68" s="3">
-        <v>-99000000</v>
-      </c>
-    </row>
-    <row r="69" spans="3:4" x14ac:dyDescent="0.3">
+        <v>-90000000</v>
+      </c>
+    </row>
+    <row r="69" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B69" t="s">
+        <v>63</v>
+      </c>
       <c r="C69" t="s">
         <v>7</v>
       </c>
       <c r="D69" s="3">
-        <v>-2000000</v>
-      </c>
-    </row>
-    <row r="70" spans="3:4" x14ac:dyDescent="0.3">
+        <v>-2103570</v>
+      </c>
+    </row>
+    <row r="70" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B70" t="s">
+        <v>63</v>
+      </c>
       <c r="C70" t="s">
         <v>35</v>
       </c>
       <c r="D70" s="3">
-        <v>-6930000</v>
-      </c>
-    </row>
-    <row r="72" spans="3:4" x14ac:dyDescent="0.3">
+        <v>-5499353</v>
+      </c>
+    </row>
+    <row r="72" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B72" t="s">
+        <v>63</v>
+      </c>
       <c r="C72" t="s">
+        <v>61</v>
+      </c>
+      <c r="D72" s="3">
+        <v>-19764096</v>
+      </c>
+    </row>
+    <row r="77" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B77" t="s">
+        <v>62</v>
+      </c>
+      <c r="C77" t="s">
         <v>42</v>
       </c>
-      <c r="D72" s="3">
+      <c r="D77" s="19">
         <v>-6000000</v>
       </c>
     </row>
-    <row r="73" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="C73" t="s">
+    <row r="78" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B78" t="s">
+        <v>62</v>
+      </c>
+      <c r="C78" t="s">
         <v>43</v>
       </c>
-      <c r="D73" s="3">
+      <c r="D78" s="19">
         <v>-4000000</v>
       </c>
     </row>
-    <row r="74" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="C74" t="s">
+    <row r="79" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B79" t="s">
+        <v>62</v>
+      </c>
+      <c r="C79" t="s">
         <v>36</v>
       </c>
-      <c r="D74" s="3">
+      <c r="D79" s="19">
         <v>-2059610</v>
       </c>
     </row>
-    <row r="75" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="C75" t="s">
+    <row r="80" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B80" t="s">
+        <v>62</v>
+      </c>
+      <c r="C80" t="s">
         <v>37</v>
       </c>
-      <c r="D75" s="3">
+      <c r="D80" s="19">
         <v>-25950</v>
       </c>
     </row>
-    <row r="76" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="C76" t="s">
+    <row r="81" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B81" t="s">
+        <v>62</v>
+      </c>
+      <c r="C81" t="s">
         <v>41</v>
       </c>
-      <c r="D76" s="3">
+      <c r="D81" s="19">
         <v>-2590</v>
       </c>
     </row>
-    <row r="77" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="C77" t="s">
+    <row r="82" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B82" t="s">
+        <v>62</v>
+      </c>
+      <c r="C82" t="s">
         <v>48</v>
       </c>
-      <c r="D77" s="3">
+      <c r="D82" s="19">
         <v>-988500</v>
       </c>
     </row>
-    <row r="78" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="C78" t="s">
+    <row r="83" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B83" t="s">
+        <v>62</v>
+      </c>
+      <c r="C83" t="s">
         <v>49</v>
       </c>
-      <c r="D78" s="3">
+      <c r="D83" s="19">
         <v>-110000</v>
       </c>
     </row>
-    <row r="79" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="C79" t="s">
+    <row r="84" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B84" t="s">
+        <v>62</v>
+      </c>
+      <c r="C84" t="s">
         <v>59</v>
       </c>
-      <c r="D79" s="15">
-        <f>-(D64+D65)*0.1</f>
-        <v>-17417244.699999999</v>
-      </c>
-    </row>
-    <row r="81" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="C81" t="s">
+      <c r="D84" s="15"/>
+    </row>
+    <row r="86" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="C86" t="s">
         <v>45</v>
       </c>
-      <c r="D81" s="16">
-        <f>SUM(D64:D79)</f>
-        <v>40638552.299999997</v>
+      <c r="D86" s="16">
+        <f>SUM(D63:D72)</f>
+        <v>52018696</v>
       </c>
     </row>
   </sheetData>

--- a/마케팅 비용 계산.xlsx
+++ b/마케팅 비용 계산.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mnbv6\Desktop\투캉 공유 폴더\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{453A4A39-9FDA-4B43-A0AA-C1641DED2B7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F9B160B-9077-4AEA-8656-712F53989B45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="20880" xr2:uid="{CAF1035B-39F7-4003-9AD6-DEFCDF622D01}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{CAF1035B-39F7-4003-9AD6-DEFCDF622D01}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="68">
   <si>
     <t>국민은행</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -254,10 +254,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>팽글</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>8월1일~8월31일</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -287,6 +283,26 @@
   </si>
   <si>
     <t>지급</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>9월1일~9월30일</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>10월1일~10월31일</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>신용보증대출</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>11월1일~11월31일</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>(예상)</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -300,7 +316,7 @@
     <numFmt numFmtId="176" formatCode="&quot;₩&quot;#,##0_);[Red]\(&quot;₩&quot;#,##0\)"/>
     <numFmt numFmtId="177" formatCode="mm&quot;월&quot;\ dd&quot;일&quot;"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -384,6 +400,27 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3C4043"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1C2B33"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF3737"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -416,7 +453,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -475,6 +512,15 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -792,7 +838,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2423A38-23FA-43A1-9DAD-825E17572FDC}">
-  <dimension ref="A2:Q86"/>
+  <dimension ref="A2:R86"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22.75" bestFit="1" customWidth="1"/>
@@ -802,14 +848,17 @@
     <col min="5" max="5" width="17.25" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14.875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="18.625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.25" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14.25" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.875" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="13.625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.625" bestFit="1" customWidth="1"/>
-    <col min="15" max="17" width="14.25" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9.25" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="19.375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="19.375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.25" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="10.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:17" x14ac:dyDescent="0.3">
@@ -1554,7 +1603,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A49" s="5">
         <v>45868</v>
       </c>
@@ -1577,7 +1626,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A50" s="5">
         <v>45869</v>
       </c>
@@ -1590,14 +1639,9 @@
       <c r="F50" s="3">
         <v>-25950</v>
       </c>
-      <c r="H50" t="s">
-        <v>55</v>
-      </c>
-      <c r="I50" s="8">
-        <v>2590995</v>
-      </c>
-    </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="I50" s="8"/>
+    </row>
+    <row r="51" spans="1:15" x14ac:dyDescent="0.3">
       <c r="E51" t="s">
         <v>41</v>
       </c>
@@ -1605,7 +1649,7 @@
         <v>-2590</v>
       </c>
     </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B52" s="7">
         <f>SUM(B22:B51)</f>
         <v>209948223</v>
@@ -1617,7 +1661,7 @@
         <v>-40000000</v>
       </c>
     </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:15" x14ac:dyDescent="0.3">
       <c r="E53" t="s">
         <v>47</v>
       </c>
@@ -1625,7 +1669,7 @@
         <v>-100000000</v>
       </c>
     </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:15" x14ac:dyDescent="0.3">
       <c r="E54" t="s">
         <v>48</v>
       </c>
@@ -1633,7 +1677,7 @@
         <v>-988500</v>
       </c>
     </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:15" x14ac:dyDescent="0.3">
       <c r="E55" t="s">
         <v>49</v>
       </c>
@@ -1641,7 +1685,7 @@
         <v>-110000</v>
       </c>
     </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:15" x14ac:dyDescent="0.3">
       <c r="E57" t="s">
         <v>45</v>
       </c>
@@ -1654,55 +1698,161 @@
       </c>
       <c r="I57" s="13">
         <f>SUM(I39:I55)</f>
-        <v>5341854</v>
-      </c>
-    </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.3">
+        <v>2750859</v>
+      </c>
+    </row>
+    <row r="62" spans="1:15" x14ac:dyDescent="0.3">
       <c r="C62" s="2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.3">
+        <v>55</v>
+      </c>
+      <c r="G62" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="K62" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="N62" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="63" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B63" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C63" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D63" s="18">
         <v>7526335</v>
       </c>
-      <c r="F63" s="3"/>
-      <c r="M63" s="8"/>
-    </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="F63" t="s">
+        <v>62</v>
+      </c>
+      <c r="G63" t="s">
+        <v>59</v>
+      </c>
+      <c r="H63" s="18">
+        <f>D86</f>
+        <v>94095859</v>
+      </c>
+      <c r="J63" t="s">
+        <v>62</v>
+      </c>
+      <c r="K63" t="s">
+        <v>59</v>
+      </c>
+      <c r="L63" s="18">
+        <f>H86</f>
+        <v>128496961</v>
+      </c>
+      <c r="N63" t="s">
+        <v>59</v>
+      </c>
+      <c r="O63" s="18">
+        <f>L86</f>
+        <v>131504084</v>
+      </c>
+    </row>
+    <row r="64" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B64" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C64" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D64" s="17">
         <v>161859380</v>
       </c>
-    </row>
-    <row r="65" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F64" t="s">
+        <v>62</v>
+      </c>
+      <c r="G64" t="s">
+        <v>56</v>
+      </c>
+      <c r="H64" s="17">
+        <v>122127418</v>
+      </c>
+      <c r="J64" t="s">
+        <v>62</v>
+      </c>
+      <c r="K64" t="s">
+        <v>56</v>
+      </c>
+      <c r="L64" s="17">
+        <v>129906363</v>
+      </c>
+      <c r="N64" t="s">
+        <v>56</v>
+      </c>
+      <c r="O64" s="17">
+        <v>63321472</v>
+      </c>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.3">
       <c r="C65" t="s">
-        <v>58</v>
-      </c>
-      <c r="E65" s="18">
+        <v>57</v>
+      </c>
+      <c r="D65" s="18">
         <v>12313067</v>
       </c>
-    </row>
-    <row r="66" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="E65" s="18"/>
+      <c r="G65" t="s">
+        <v>57</v>
+      </c>
+      <c r="H65" s="17">
+        <v>8632114</v>
+      </c>
+      <c r="K65" t="s">
+        <v>57</v>
+      </c>
+      <c r="L65" s="17">
+        <v>11804731</v>
+      </c>
+      <c r="N65" t="s">
+        <v>57</v>
+      </c>
+      <c r="O65" s="17">
+        <v>6500000</v>
+      </c>
+      <c r="P65" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.3">
       <c r="C66" t="s">
         <v>50</v>
       </c>
-      <c r="D66" s="18"/>
-    </row>
-    <row r="68" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="D66" s="18">
+        <v>10000000</v>
+      </c>
+      <c r="G66" t="s">
+        <v>50</v>
+      </c>
+      <c r="H66" s="18">
+        <v>5000000</v>
+      </c>
+      <c r="K66" t="s">
+        <v>50</v>
+      </c>
+      <c r="L66" s="18">
+        <v>5000000</v>
+      </c>
+      <c r="N66" t="s">
+        <v>50</v>
+      </c>
+      <c r="O66" s="18">
+        <v>5000000</v>
+      </c>
+      <c r="Q66" s="20"/>
+      <c r="R66" s="20"/>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="Q67" s="21"/>
+      <c r="R67" s="21"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B68" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C68" t="s">
         <v>16</v>
@@ -1710,10 +1860,36 @@
       <c r="D68" s="3">
         <v>-90000000</v>
       </c>
-    </row>
-    <row r="69" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F68" t="s">
+        <v>62</v>
+      </c>
+      <c r="G68" t="s">
+        <v>16</v>
+      </c>
+      <c r="H68" s="3">
+        <v>-75144509</v>
+      </c>
+      <c r="J68" t="s">
+        <v>62</v>
+      </c>
+      <c r="K68" t="s">
+        <v>16</v>
+      </c>
+      <c r="L68" s="3">
+        <v>-86125376</v>
+      </c>
+      <c r="N68" t="s">
+        <v>16</v>
+      </c>
+      <c r="O68" s="3">
+        <v>-43513321</v>
+      </c>
+      <c r="Q68" s="7"/>
+      <c r="R68" s="7"/>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B69" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C69" t="s">
         <v>7</v>
@@ -1721,10 +1897,34 @@
       <c r="D69" s="3">
         <v>-2103570</v>
       </c>
-    </row>
-    <row r="70" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F69" t="s">
+        <v>62</v>
+      </c>
+      <c r="G69" t="s">
+        <v>7</v>
+      </c>
+      <c r="H69" s="3">
+        <v>-1363290</v>
+      </c>
+      <c r="J69" t="s">
+        <v>62</v>
+      </c>
+      <c r="K69" t="s">
+        <v>7</v>
+      </c>
+      <c r="L69" s="3">
+        <v>-1748759</v>
+      </c>
+      <c r="N69" t="s">
+        <v>7</v>
+      </c>
+      <c r="O69" s="3">
+        <v>-1239490</v>
+      </c>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B70" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C70" t="s">
         <v>35</v>
@@ -1732,21 +1932,67 @@
       <c r="D70" s="3">
         <v>-5499353</v>
       </c>
-    </row>
-    <row r="72" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F70" t="s">
+        <v>62</v>
+      </c>
+      <c r="G70" t="s">
+        <v>35</v>
+      </c>
+      <c r="H70" s="3">
+        <v>-5086535</v>
+      </c>
+      <c r="J70" t="s">
+        <v>62</v>
+      </c>
+      <c r="K70" t="s">
+        <v>35</v>
+      </c>
+      <c r="L70" s="3">
+        <v>-5829836</v>
+      </c>
+      <c r="N70" t="s">
+        <v>35</v>
+      </c>
+      <c r="O70" s="3">
+        <v>-3045932</v>
+      </c>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B72" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C72" t="s">
-        <v>61</v>
-      </c>
-      <c r="D72" s="3">
+        <v>60</v>
+      </c>
+      <c r="D72" s="22">
+        <v>0</v>
+      </c>
+      <c r="F72" t="s">
+        <v>62</v>
+      </c>
+      <c r="G72" t="s">
+        <v>60</v>
+      </c>
+      <c r="H72" s="3">
         <v>-19764096</v>
       </c>
-    </row>
-    <row r="77" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="J72" t="s">
+        <v>62</v>
+      </c>
+      <c r="K72" t="s">
+        <v>65</v>
+      </c>
+      <c r="L72" s="3">
+        <v>-50000000</v>
+      </c>
+      <c r="N72" t="s">
+        <v>65</v>
+      </c>
+      <c r="O72" s="3"/>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B77" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C77" t="s">
         <v>42</v>
@@ -1754,10 +2000,34 @@
       <c r="D77" s="19">
         <v>-6000000</v>
       </c>
-    </row>
-    <row r="78" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F77" t="s">
+        <v>61</v>
+      </c>
+      <c r="G77" t="s">
+        <v>42</v>
+      </c>
+      <c r="H77" s="19">
+        <v>-6000000</v>
+      </c>
+      <c r="J77" t="s">
+        <v>61</v>
+      </c>
+      <c r="K77" t="s">
+        <v>42</v>
+      </c>
+      <c r="L77" s="19">
+        <v>-6000000</v>
+      </c>
+      <c r="N77" t="s">
+        <v>42</v>
+      </c>
+      <c r="O77" s="19">
+        <v>-6000000</v>
+      </c>
+    </row>
+    <row r="78" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B78" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C78" t="s">
         <v>43</v>
@@ -1765,10 +2035,34 @@
       <c r="D78" s="19">
         <v>-4000000</v>
       </c>
-    </row>
-    <row r="79" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F78" t="s">
+        <v>61</v>
+      </c>
+      <c r="G78" t="s">
+        <v>43</v>
+      </c>
+      <c r="H78" s="19">
+        <v>-4000000</v>
+      </c>
+      <c r="J78" t="s">
+        <v>61</v>
+      </c>
+      <c r="K78" t="s">
+        <v>43</v>
+      </c>
+      <c r="L78" s="19">
+        <v>-4000000</v>
+      </c>
+      <c r="N78" t="s">
+        <v>43</v>
+      </c>
+      <c r="O78" s="19">
+        <v>-4000000</v>
+      </c>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B79" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C79" t="s">
         <v>36</v>
@@ -1776,10 +2070,34 @@
       <c r="D79" s="19">
         <v>-2059610</v>
       </c>
-    </row>
-    <row r="80" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F79" t="s">
+        <v>61</v>
+      </c>
+      <c r="G79" t="s">
+        <v>36</v>
+      </c>
+      <c r="H79" s="19">
+        <v>-2059610</v>
+      </c>
+      <c r="J79" t="s">
+        <v>61</v>
+      </c>
+      <c r="K79" t="s">
+        <v>36</v>
+      </c>
+      <c r="L79" s="19">
+        <v>-2059610</v>
+      </c>
+      <c r="N79" t="s">
+        <v>36</v>
+      </c>
+      <c r="O79" s="19">
+        <v>-2059610</v>
+      </c>
+    </row>
+    <row r="80" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B80" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C80" t="s">
         <v>37</v>
@@ -1787,10 +2105,34 @@
       <c r="D80" s="19">
         <v>-25950</v>
       </c>
-    </row>
-    <row r="81" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="F80" t="s">
+        <v>61</v>
+      </c>
+      <c r="G80" t="s">
+        <v>37</v>
+      </c>
+      <c r="H80" s="19">
+        <v>-25950</v>
+      </c>
+      <c r="J80" t="s">
+        <v>61</v>
+      </c>
+      <c r="K80" t="s">
+        <v>37</v>
+      </c>
+      <c r="L80" s="19">
+        <v>-25950</v>
+      </c>
+      <c r="N80" t="s">
+        <v>37</v>
+      </c>
+      <c r="O80" s="19">
+        <v>-25950</v>
+      </c>
+    </row>
+    <row r="81" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B81" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C81" t="s">
         <v>41</v>
@@ -1798,10 +2140,34 @@
       <c r="D81" s="19">
         <v>-2590</v>
       </c>
-    </row>
-    <row r="82" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="F81" t="s">
+        <v>61</v>
+      </c>
+      <c r="G81" t="s">
+        <v>41</v>
+      </c>
+      <c r="H81" s="19">
+        <v>-2590</v>
+      </c>
+      <c r="J81" t="s">
+        <v>61</v>
+      </c>
+      <c r="K81" t="s">
+        <v>41</v>
+      </c>
+      <c r="L81" s="19">
+        <v>-2590</v>
+      </c>
+      <c r="N81" t="s">
+        <v>41</v>
+      </c>
+      <c r="O81" s="19">
+        <v>-2590</v>
+      </c>
+    </row>
+    <row r="82" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B82" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C82" t="s">
         <v>48</v>
@@ -1809,10 +2175,34 @@
       <c r="D82" s="19">
         <v>-988500</v>
       </c>
-    </row>
-    <row r="83" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="F82" t="s">
+        <v>61</v>
+      </c>
+      <c r="G82" t="s">
+        <v>48</v>
+      </c>
+      <c r="H82" s="19">
+        <v>-988500</v>
+      </c>
+      <c r="J82" t="s">
+        <v>61</v>
+      </c>
+      <c r="K82" t="s">
+        <v>48</v>
+      </c>
+      <c r="L82" s="19">
+        <v>-988500</v>
+      </c>
+      <c r="N82" t="s">
+        <v>48</v>
+      </c>
+      <c r="O82" s="19">
+        <v>-988500</v>
+      </c>
+    </row>
+    <row r="83" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B83" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C83" t="s">
         <v>49</v>
@@ -1820,23 +2210,86 @@
       <c r="D83" s="19">
         <v>-110000</v>
       </c>
-    </row>
-    <row r="84" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="F83" t="s">
+        <v>61</v>
+      </c>
+      <c r="G83" t="s">
+        <v>49</v>
+      </c>
+      <c r="H83" s="19">
+        <v>-110000</v>
+      </c>
+      <c r="J83" t="s">
+        <v>61</v>
+      </c>
+      <c r="K83" t="s">
+        <v>49</v>
+      </c>
+      <c r="L83" s="19">
+        <v>-110000</v>
+      </c>
+      <c r="N83" t="s">
+        <v>49</v>
+      </c>
+      <c r="O83" s="19">
+        <v>-110000</v>
+      </c>
+    </row>
+    <row r="84" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B84" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C84" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D84" s="15"/>
-    </row>
-    <row r="86" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="F84" t="s">
+        <v>61</v>
+      </c>
+      <c r="G84" t="s">
+        <v>58</v>
+      </c>
+      <c r="H84" s="15"/>
+      <c r="J84" t="s">
+        <v>61</v>
+      </c>
+      <c r="K84" t="s">
+        <v>58</v>
+      </c>
+      <c r="L84" s="15"/>
+      <c r="N84" t="s">
+        <v>58</v>
+      </c>
+      <c r="O84" s="15"/>
+    </row>
+    <row r="86" spans="2:15" x14ac:dyDescent="0.3">
       <c r="C86" t="s">
         <v>45</v>
       </c>
       <c r="D86" s="16">
         <f>SUM(D63:D72)</f>
-        <v>52018696</v>
+        <v>94095859</v>
+      </c>
+      <c r="G86" t="s">
+        <v>45</v>
+      </c>
+      <c r="H86" s="16">
+        <f>SUM(H63:H72)</f>
+        <v>128496961</v>
+      </c>
+      <c r="K86" t="s">
+        <v>45</v>
+      </c>
+      <c r="L86" s="16">
+        <f>SUM(L63:L72)</f>
+        <v>131504084</v>
+      </c>
+      <c r="N86" t="s">
+        <v>45</v>
+      </c>
+      <c r="O86" s="16">
+        <f>SUM(O63:O72)</f>
+        <v>158526813</v>
       </c>
     </row>
   </sheetData>
